--- a/business_forms/025_safety_inspection_outcomes_report_form--business_forms.xlsx
+++ b/business_forms/025_safety_inspection_outcomes_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>next_steps_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Next Steps</t>
+          <t>Next Steps 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>followup_safety_standards</t>
+          <t>followup_safety_standards_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Follow-up Safety Standards</t>
+          <t>Followup Safety Standards 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>followup_outcome</t>
+          <t>followup_outcome_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Follow-up Outcome</t>
+          <t>Followup Outcome 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>followup_location</t>
+          <t>followup_location_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Follow-up Location</t>
+          <t>Followup Location 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>followup_safety_standards_choices</t>
+          <t>followup_safety_standards_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>followup_safety_standards_choices</t>
+          <t>followup_safety_standards_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>followup_safety_standards_choices</t>
+          <t>followup_safety_standards_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>followup_outcome_choices</t>
+          <t>followup_outcome_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>followup_outcome_choices</t>
+          <t>followup_outcome_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
